--- a/data/excel/acciones_energia.xlsx
+++ b/data/excel/acciones_energia.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2514"/>
+  <dimension ref="A1:E2515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur (TGS) (TGS, Nueva York), precio de cierre en dólares</t>
+          <t>Transportadora de Gas del Sur (TGS, Nueva York), precio de cierre en dólares</t>
         </is>
       </c>
     </row>
@@ -41807,6 +41807,23 @@
       </c>
       <c r="E2514" t="n">
         <v>25.3</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="2" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>25.02</v>
       </c>
     </row>
   </sheetData>
@@ -41867,7 +41884,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://api.nasdaq.com/api/quote/YPF/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-29&amp;limit=9999 https://api.nasdaq.com/api/quote/VIST/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-29&amp;limit=9999 https://api.nasdaq.com/api/quote/PAM/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-29&amp;limit=9999 https://api.nasdaq.com/api/quote/TGS/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-29&amp;limit=9999</t>
+          <t>https://api.nasdaq.com/api/quote/YPF/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999 https://api.nasdaq.com/api/quote/VIST/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999 https://api.nasdaq.com/api/quote/PAM/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999 https://api.nasdaq.com/api/quote/TGS/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999</t>
         </is>
       </c>
     </row>
@@ -41879,7 +41896,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29T12:36:56Z</t>
+          <t>2026-10-30T06:28:30Z</t>
         </is>
       </c>
     </row>
@@ -41891,7 +41908,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/data/excel/acciones_energia.xlsx
+++ b/data/excel/acciones_energia.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2515"/>
+  <dimension ref="A1:E2516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41824,6 +41824,23 @@
       </c>
       <c r="E2515" t="n">
         <v>25.02</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="2" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>47</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>23.67</v>
       </c>
     </row>
   </sheetData>
@@ -41884,7 +41901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://api.nasdaq.com/api/quote/YPF/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999 https://api.nasdaq.com/api/quote/VIST/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999 https://api.nasdaq.com/api/quote/PAM/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999 https://api.nasdaq.com/api/quote/TGS/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-30&amp;limit=9999</t>
+          <t>https://api.nasdaq.com/api/quote/YPF/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-31&amp;limit=9999 https://api.nasdaq.com/api/quote/VIST/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-31&amp;limit=9999 https://api.nasdaq.com/api/quote/PAM/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-31&amp;limit=9999 https://api.nasdaq.com/api/quote/TGS/historical?assetclass=stocks&amp;fromdate=2016-01-01&amp;todate=2026-10-31&amp;limit=9999</t>
         </is>
       </c>
     </row>
@@ -41896,7 +41913,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:30Z</t>
+          <t>2026-10-31T06:18:29Z</t>
         </is>
       </c>
     </row>
@@ -41908,7 +41925,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
